--- a/太空战舰.xlsx
+++ b/太空战舰.xlsx
@@ -2,14 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>
@@ -569,19 +564,19 @@
     <t>正电子聚焦装置</t>
   </si>
   <si>
-    <t>提高所有能量武器的伤害，效果为原伤害*（1+para1*等级）向上取整.</t>
+    <t>提高所有武器的伤害，效果为原伤害*（1+para1)^等级向上取整.</t>
   </si>
   <si>
-    <t>能量武器伤害提高{para1*等级}</t>
+    <t>所有武器伤害提高{(1+para1)^等级,百分比显示,保留两位小数,即100.3%展示为100%}</t>
   </si>
   <si>
     <t>简并态装甲</t>
   </si>
   <si>
-    <t>armour当前值增加（1+para1*等级），向上取整。</t>
+    <t>生命和护盾最大值增加（1+para1）^等级，向上取整。</t>
   </si>
   <si>
-    <t>生命增加{para1*等级}</t>
+    <t>生命增加{（1+para1）^等级,百分比显示,保留两位小数,即100.3%展示为100%}</t>
   </si>
 </sst>
 </file>
@@ -1520,9 +1515,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:D67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <sheetData>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
@@ -2022,11 +2017,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F73"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="78.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="78.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3707,15 +3702,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:N506"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="4" max="5" width="9" customWidth="1"/>
-    <col min="9" max="11" width="10.2222222222222" customWidth="1"/>
-    <col min="12" max="12" width="11.7777777777778"/>
+    <col min="9" max="11" width="10.225" customWidth="1"/>
+    <col min="12" max="12" width="11.775"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -25317,16 +25312,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="14.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="30.2222222222222" customWidth="1"/>
-    <col min="4" max="4" width="10.1111111111111" customWidth="1"/>
-    <col min="5" max="5" width="11.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="17.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="14.1083333333333" customWidth="1"/>
+    <col min="2" max="2" width="15.225" customWidth="1"/>
+    <col min="3" max="3" width="30.225" customWidth="1"/>
+    <col min="4" max="4" width="10.1083333333333" customWidth="1"/>
+    <col min="5" max="5" width="11.8916666666667" customWidth="1"/>
+    <col min="7" max="7" width="17.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -25571,12 +25566,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="62.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="15.225" customWidth="1"/>
+    <col min="3" max="3" width="62.775" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -25708,9 +25703,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -25760,9 +25755,9 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -25882,11 +25877,11 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
+    <col min="1" max="1" width="16.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
